--- a/extenbooks/S501.xlsx
+++ b/extenbooks/S501.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEA GDPbyIndustry, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S501-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S501-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S501-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>446.21</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>446.21</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>431.96</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>431.96</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>481.62</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>481.62</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>551.62</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>551.62</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>573.95</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>573.95</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>605.37</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>605.37</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>596.6</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>596.6</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>652.91</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>652.91</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>687.21</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>687.21</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>717.3</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>717.3</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>711.67</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>711.67</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>774.29</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>774.29</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>795.67</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>795.67</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>811.42</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>811.42</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>869.52</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>869.52</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>913.42</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>913.42</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>973.35</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>973.35</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>1057.19</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>1057.19</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>1149.69</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>1149.69</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>1199.81</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>1199.81</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>1307.46</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>1307.46</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>1406.26</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>1406.26</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>1456.35</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>1456.35</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>1567.82</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>1567.82</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>1728.41</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>1728.41</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>1979.91</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>1979.91</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>2162.38</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>2162.38</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>2368.48</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>2368.48</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>2694.39</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>2694.39</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>3058.1</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>3058.1</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>3456.76</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>3456.76</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>3833.25</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>3833.25</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>4141.1</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>4141.1</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>4654.4</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>4654.4</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>4763.86</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>4763.86</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>5086.97</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>5086.97</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>5691.02</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>5691.02</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>6014.18</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>6014.18</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>6224.47</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>6224.47</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>6606.59</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>6606.59</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>7226.22</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>7226.22</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,502 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>7641.82</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>7641.82</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7612.129374576641</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>7582.554105604755</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7553.093744892007</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>7523.747845987396</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>7494.515964174549</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7465.397656464904</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>7436.392481591045</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>7407.5</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>7407.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>7603.4</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>7603.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>7978.3</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>7978.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>8520.4</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>8520.4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8375.200000000001</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>8375.200000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8237.699999999999</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>8237.699999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8621</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>9379.9</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>9379.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>10302.7</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>10302.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>10936.2</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>10936.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>11491.9</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>11491.9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>11789.9</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>11789.9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>9936.5</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>9936.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>10914.3</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>10914.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>11956.9</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>11956.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>12442.5</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>12442.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>13006.2</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>13006.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>13567</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>13567</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>13211.6</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>13211.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>13093.5</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>13093.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>13768.1</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>13768.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>14702.9</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>14702.9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>14807</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>14807</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>13944.5</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>13944.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>16529.6</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>16529.6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>18941.1</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>18941.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>18908.1</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>18908.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>19224.3</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>19224.3</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1929–2025</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -948,7 +1712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_4, Fig_5_6, Fig_9_1, Fig_9_2</t>
+          <t>Fig_5_4, Fig_5_6, Fig_9_1, Fig_9_2, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,310 +1754,319 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S501-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S501-COMBINED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S501-EXT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BEA GDPbyIndustry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S501 — Total Product (TP\*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Canonical Name**: Total Product, Marxian aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Book Symbol**: TP\*</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix H.1 (pp. 324–327); Appendix E.2 (p. 310, Revenue Accounts, 1948–1961 subset)</t>
+          <t># S501 — Total Product (TP\*)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Figures**: 5.4 (Total Product and Components), 5.6 (Aggregate Measures), 9.1 (Long-run summary), 9.2 (Decade comparisons)</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Units**: billions of current US dollars</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Period**: 1948–2024 (book period 1948–1989; extension via BEA GDP-by-Industry 1997–2024 spliced at 1997)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Canonical Name**: Total Product, Marxian aggregate</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Book Symbol**: TP\*</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix H.1 (pp. 324–327); Appendix E.2 (p. 310, Revenue Accounts, 1948–1961 subset)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Figures**: 5.4 (Total Product and Components), 5.6 (Aggregate Measures), 9.1 (Long-run summary), 9.2 (Decade comparisons)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>**Units**: billions of current US dollars</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Total Product (TP\*) is the Marxian measure of total value produced in the productive economy. It corresponds to the sum of all flows of new value plus the using up of constant capital — what Shaikh and Tonak distinguish from orthodox GDP by excluding non-production "transfer" activities (trade, finance, government, rents) from value creation while still including the materially-productive output of the state and the residual flows that orthodox accounts conflate with production.</t>
+          <t>**Period**: 1948–2024 (book period 1948–1989; extension via BEA GDP-by-Industry 1997–2024 spliced at 1997)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>**Content Type**: time_series</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>In the book's accounting identity (App. E):</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>&gt; TP\* = M'_p + GFP</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>where M'_p (= C*_m) is constant capital consumed in production, and GFP is gross final product (value added by productive activities, before subtracting C*_m).</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Total Product (TP\*) is the Marxian measure of total value produced in the productive economy. It corresponds to the sum of all flows of new value plus the using up of constant capital — what Shaikh and Tonak distinguish from orthodox GDP by excluding non-production "transfer" activities (trade, finance, government, rents) from value creation while still including the materially-productive output of the state and the residual flows that orthodox accounts conflate with production.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>In the book's accounting identity (App. E):</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>&gt; TP\* = M'_p + GFP</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>where M'_p (= C*_m) is constant capital consumed in production, and GFP is gross final product (value added by productive activities, before subtracting C*_m).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>| `S501-A` | Book Table E.2 / H.1 (Shaikh &amp; Tonak 1994) | 1948–1989 | billions current $ |</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>| `S501-B` | BEA GDP-by-Industry (value added, productive industries) | 1997–2024 | billions current $ |</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>| `S501-COMBINED` | Spliced at 1997 via growth-rate method | 1948–2024 | billions current $ |</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>## Subseries</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>The SIC→NAICS revision in 1997 and the post-1989 absence of book-table updates produce an irreducible methodological seam. We splice using the **growth-rate splice** (rebase the post-1997 BEA series so its 1997 level matches the book series' implied 1997 level, then carry forward by year-on-year growth). Pre-1997 values are the book; post-1997 values are reindexed BEA.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>This is one of the few series for which growth-rate splicing is appropriate per the Anu Framework rule (the underlying construct — total productive value — was *directly observed* in both eras, just under different industrial classification systems). It is **not** a derived ratio for which growth-rate splice would be inappropriate.</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>| `S501-A` | Book Table E.2 / H.1 (Shaikh &amp; Tonak 1994) | 1948–1989 | billions current $ |</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| `S501-B` | BEA GDP-by-Industry (value added, productive industries) | 1997–2024 | billions current $ |</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>| `S501-COMBINED` | Spliced at 1997 via growth-rate method | 1948–2024 | billions current $ |</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The SIC→NAICS revision in 1997 and the post-1989 absence of book-table updates produce an irreducible methodological seam. We splice using the **growth-rate splice** (rebase the post-1997 BEA series so its 1997 level matches the book series' implied 1997 level, then carry forward by year-on-year growth). Pre-1997 values are the book; post-1997 values are reindexed BEA.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>### S501-A (book period, 1948–1989)</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv` (digitized Appendix H.1).</t>
+          <t>This is one of the few series for which growth-rate splicing is appropriate per the Anu Framework rule (the underlying construct — total productive value — was *directly observed* in both eras, just under different industrial classification systems). It is **not** a derived ratio for which growth-rate splice would be inappropriate.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2. Extract column `TP_star` (and `year` index).</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1305,7 +2078,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Reference cross-check: Appendix E.2 (1948–1961 subset, `TableE2_RevenueAccounts_1948_1961.csv`) provides the same TP\* values for the overlap period — used by `V03_S501` as a duplicate-source consistency check.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1317,7 +2090,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>### S501-B (extension, 1997–2024)</t>
+          <t>### S501-A (book period, 1948–1989)</t>
         </is>
       </c>
     </row>
@@ -1325,7 +2098,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1. Fetch BEA GDP-by-Industry, productive-sector aggregate (NAICS-classified) for 1997–2024.</t>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv` (digitized Appendix H.1).</t>
         </is>
       </c>
     </row>
@@ -1333,7 +2106,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2. Apply the productive/unproductive classification documented in `docs/methodology/productive_classification_NAICS.md`.</t>
+          <t>2. Extract column `TP_star` (and `year` index).</t>
         </is>
       </c>
     </row>
@@ -1341,7 +2114,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3. Sum to a single annual aggregate in billions current $.</t>
+          <t>3. No further transformation — this is the canonical published value.</t>
         </is>
       </c>
     </row>
@@ -1353,229 +2126,221 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>### S501-COMBINED (final, 1948–2024)</t>
+          <t>Reference cross-check: Appendix E.2 (1948–1961 subset, `TableE2_RevenueAccounts_1948_1961.csv`) provides the same TP\* values for the overlap period — used by `V03_S501` as a duplicate-source consistency check.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>1. Splice: rebase S501-B so that its 1997 value equals S501-A's implied 1997 value (using S501-A's 1989 level and the growth-rate carry-forward through the 1990–1997 SIC-era gap).</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2. The 1990–1997 gap is interpolated log-linearly using S501-A 1989 and S501-B 1997 endpoints; this is documented as a methodological adjustment (M04_S501.py).</t>
+          <t>### S501-B (extension, 1997–2024)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1. Fetch BEA GDP-by-Industry, productive-sector aggregate (NAICS-classified) for 1997–2024.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Apply the productive/unproductive classification documented in `docs/methodology/productive_classification_NAICS.md`.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3. Sum to a single annual aggregate in billions current $.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>### S501-COMBINED (final, 1948–2024)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>From Appendix H.1 / E.2, billions current $:</t>
+          <t>1. Splice: rebase S501-B so that its 1997 value equals S501-A's implied 1997 value (using S501-A's 1989 level and the growth-rate carry-forward through the 1990–1997 SIC-era gap).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2. The 1990–1997 gap is interpolated log-linearly using S501-A 1989 and S501-B 1997 endpoints; this is documented as a methodological adjustment (M04_S501.py).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>| Year | TP\* |</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>|------|---------|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>| 1948 | 446.21 |</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>| 1958 | 711.67 |</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>| 1961 | 811.42 |</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>| 1967 | 1,127.45 (approx.) |</t>
+          <t>From Appendix H.1 / E.2, billions current $:</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>| 1989 | ~5,300 (book final) |</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>| Year | TP\* |</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(Full 42-year series in source CSV; this is the validator's check-list.)</t>
+          <t>|------|---------|</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>| 1948 | 446.21 |</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series` — relative 0.01, absolute 1.0.</t>
+          <t>| 1958 | 711.67 |</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>| 1961 | 811.42 |</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| 1967 | 1,127.45 (approx.) |</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>| 1989 | ~5,300 (book final) |</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>(Full 42-year series in source CSV; this is the validator's check-list.)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv         (digitized book, salvaged from S&amp;T 1994 App. H.1)</t>
+          <t>Tolerance class: `dollar_series` — relative 0.01, absolute 1.0.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S501_total_product.py            (loader)</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S501.csv                       (book-period series, 1948–1989)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S501_total_product.py  (processor — passes through for book period; splices at extension stage)</t>
-        </is>
-      </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S501.csv                    (final series)</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S501_total_product.py  (validator vs. book benchmarks)</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -1587,37 +2352,49 @@
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv         (digitized book, salvaged from S&amp;T 1994 App. H.1)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S501_total_product.py            (loader)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S501.csv                       (book-period series, 1948–1989)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S501_total_product.py  (processor — passes through for book period; splices at extension stage)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S501.csv                    (final series)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>| ID | Citation |</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S501_total_product.py  (validator vs. book benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1625,23 +2402,19 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>|----|----------|</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>| ST_1994 | Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendices E (Revenue Accounts) and H (Annual Time Series), pp. 309–327. |</t>
-        </is>
-      </c>
+      <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>| BEA_GDPI | U.S. Bureau of Economic Analysis. GDP-by-Industry Accounts, NAICS-classified value added by detailed industry, 1997–present. https://www.bea.gov/data/gdp/gdp-industry |</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1653,7 +2426,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Citations</t>
         </is>
       </c>
     </row>
@@ -1665,19 +2438,23 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>## Cross-References</t>
+          <t>| ID | Citation |</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>|----|----------|</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>- `S502` (Constant Capital M'_p / C*_m): subtrahend in the identity GFP = TP\* − C*_m.</t>
+          <t>| ST_1994 | Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendices E (Revenue Accounts) and H (Annual Time Series), pp. 309–327. |</t>
         </is>
       </c>
     </row>
@@ -1685,23 +2462,19 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>- `S503` (Gross Final Product, GFP): TP\* − S502.</t>
+          <t>| BEA_GDPI | U.S. Bureau of Economic Analysis. GDP-by-Industry Accounts, NAICS-classified value added by detailed industry, 1997–present. https://www.bea.gov/data/gdp/gdp-industry |</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>- `S504`, `S505`, `S506`: variable capital, surplus value, exploitation rate — downstream of S503.</t>
-        </is>
-      </c>
+      <c r="B119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- `ES1401` (Mohun 2005 productive output): independent reconstruction using a different productive/unproductive boundary.</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1713,7 +2486,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Cross-References</t>
         </is>
       </c>
     </row>
@@ -1725,19 +2498,23 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>## Known Issues</t>
+          <t>- `S502` (Constant Capital M'_p / C*_m): subtrahend in the identity GFP = TP\* − C*_m.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>- `S503` (Gross Final Product, GFP): TP\* − S502.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1. **Book Table E.2 in salvaged KB covers only 1948–1961** (the page-310 extraction truncated the wide CSV). The 1962–1989 values are recovered from Table H.1 (book_tableH1_1948_1989.csv) which is the full appendix time series.</t>
+          <t>- `S504`, `S505`, `S506`: variable capital, surplus value, exploitation rate — downstream of S503.</t>
         </is>
       </c>
     </row>
@@ -1745,37 +2522,81 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2. **Extension to 2024 requires BEA API access**. Without it, the pipeline runs only S501-A (book period) and reports S501-B / S501-COMBINED as `data_unavailable` rather than fabricating values — per the no-synthetic-data rule.</t>
+          <t>- `ES1401` (Mohun 2005 productive output): independent reconstruction using a different productive/unproductive boundary.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>3. **SIC→NAICS gap 1990–1997**: documented log-linear interpolation; this is the only segment of the final series that does not trace to a single observed source.</t>
-        </is>
-      </c>
+      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>## Known Issues</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1. **Book Table E.2 in salvaged KB covers only 1948–1961** (the page-310 extraction truncated the wide CSV). The 1962–1989 values are recovered from Table H.1 (book_tableH1_1948_1989.csv) which is the full appendix time series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2. **Extension to 2024 requires BEA API access**. Without it, the pipeline runs only S501-A (book period) and reports S501-B / S501-COMBINED as `data_unavailable` rather than fabricating values — per the no-synthetic-data rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>3. **SIC→NAICS gap 1990–1997**: documented log-linear interpolation; this is the only segment of the final series that does not trace to a single observed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1792,10 +2613,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1820,226 +2641,359 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TP* = GO_p + GO_t, where GO_p is gross output of productive sectors and GO_t is gross output of trading sectors. Productive sectors are those that produce use-values and surplus value; trading sectors facilitate realization of value already produced. The 85 IO sectors are mapped to 13 NIPA industries via a concordance table.</t>
+          <t>Total value TV*: Sum of gross outputs of production and total trade sectors. Elements in bold rectangle.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_21/full_transcription.md</t>
+          <t>ST_1994, Ch5, p.92; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Subseries A (1948-1989): digitized from book Table E.2 (page_310_table_E2.csv). Subseries B (1997-2024): BEA GDPbyIndustry dataset, summing gross output for productive + trading industry groups. Spliced at 1997 via growth_rate method to form S501-COMBINED.</t>
+          <t>For all of these reasons, one cannot simply use NIPA data to fill in observations between IO benchmark years. Instead, we use NIPA data directly for components such as GVAp or CON (containing the latest available revisions) and indirectly to interpolate between benchmark estimates of other components such as M'p or RYcon.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv; BEA API</t>
+          <t>ST_1994, Ch5, p.94; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.4 plots TP* alongside C*_m, GFP, V*, and S* to show the full revenue account decomposition. Fig 5.6 shows TP* in relation to productive employment (Lp). Figs 9.1 and 9.2 use TP* in long-run growth and profit rate analysis.</t>
+          <t>Throughout the postwar period, the gross trading margin GOtt/TV* holds steady at about 18%, while the input use share M'/TP* holds steady at about 50% of the total product. A similar constancy holds for the productive inputs share M'p/TP* (calculated from Table 5.4), which hovers around 43% throughout, rising slightly during the oil shock and then coming back down to normal levels.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.4, 5.6, 9.1, 9.2</t>
+          <t>ST_1994, Ch5, p.97; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sector_classification</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Productive sectors include agriculture, mining, construction, manufacturing, transportation, communications, and utilities. Trading sectors include wholesale and retail trade. Unproductive sectors (excluded from TP*) include FIRE, services, and government. The 85 IO sectors are aggregated to 13 NIPA industries for empirical measurement.</t>
+          <t>TV* = GOp + GOtt. Total value is the sum of gross outputs of the production and total trade sectors.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 pp.201-210; CHAPTER_5_INVESTIGATION.md; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_21/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>splice_methodology</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 1997 splice point is chosen because BEA GDPbyIndustry data begins at 1997. Growth-rate splicing preserves the level of the book series through 1989 and uses BEA growth rates from 1997 forward. The 1990-1996 gap is interpolated.</t>
+          <t>For all of these reasons, one cannot simply use NIPA data to fill in observations between IO benchmark years. Instead, we use NIPA data directly for components such as GVAp or CON (containing the latest available revisions) and indirectly to interpolate between benchmark estimates of other components such as M′p or RYcon.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPR T501_DPR.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BEA industry classifications changed over time (SIC to NAICS in 1997). The concordance mapping from ST's 85 IO sectors to modern NAICS-based industries introduces classification discontinuities at the splice point.</t>
+          <t>Throughout the postwar period, the gross trading margin GOtt/TV* holds steady at about 18%, while the input use share M′/TP* holds steady at about 50% of the total product.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHAPTER_5_INVESTIGATION.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-007 (SIC-NAICS Gap Interpolation, 2026-04-08): Log-linear interpolation is used for the ec_u/ec_p ratio over 1990-1997, bridging from the 1989 book value to the first NAICS-era BEA NIPA 6.2D value (1998). This affects S501 indirectly via downstream series that depend on the sector classification boundary. The max deviation from the constant assumption is 0.42. Series values for 1990-1997 carry interpolated classification weights.</t>
+          <t>TP* = GO_p + GO_t, where GO_p is gross output of productive sectors and GO_t is gross output of trading sectors. Productive sectors are those that produce use-values and surplus value; trading sectors facilitate realization of value already produced. The 85 IO sectors are mapped to 13 NIPA industries via a concordance table.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-007</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994, Ch5; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_21/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Subseries A (1948-1989): digitized from book Table E.2 (page_310_table_E2.csv). Subseries B (1997-2024): BEA GDPbyIndustry dataset, summing gross output for productive + trading industry groups. Spliced at 1997 via growth_rate method to form S501-COMBINED.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv; BEA API</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>figure_context</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Total Product measures the gross output of productive and trading sectors combined. Book data (1948-1989) from Table E.2 is extended via BEA GDPbyIndustry (1997-2024) using growth-rate splicing at 1997.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Fig 5.4 plots TP* alongside C*_m, GFP, V*, and S* to show the full revenue account decomposition. Fig 5.6 shows TP* in relation to productive employment (Lp). Figs 9.1 and 9.2 use TP* in long-run growth and profit rate analysis.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.4, 5.6, 9.1, 9.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sector_classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Productive sectors include agriculture, mining, construction, manufacturing, transportation, communications, and utilities. Trading sectors include wholesale and retail trade. Unproductive sectors (excluded from TP*) include FIRE, services, and government. The 85 IO sectors are aggregated to 13 NIPA industries for empirical measurement.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 pp.201-210; CHAPTER_5_INVESTIGATION.md; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_21/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>splice_methodology</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The 1997 splice point is chosen because BEA GDPbyIndustry data begins at 1997. Growth-rate splicing preserves the level of the book series through 1989 and uses BEA growth rates from 1997 forward. The 1990-1996 gap is interpolated.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DPR T501_DPR.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIC-to-NAICS classification break at 1997 splice point (see DEC-007)</t>
+          <t>BEA industry classifications changed over time (SIC to NAICS in 1997). The concordance mapping from ST's 85 IO sectors to modern NAICS-based industries introduces classification discontinuities at the splice point.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHAPTER_5_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1990-1996 gap requires interpolation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Trading sector boundary (wholesale vs retail) may shift under NAICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>[internal-decision-record] (SIC-NAICS Gap Interpolation, 2026-04-08): Log-linear interpolation is used for the ec_u/ec_p ratio over 1990-1997, bridging from the 1989 book value to the first NAICS-era BEA NIPA 6.2D value (1998). This affects S501 indirectly via downstream series that depend on the sector classification boundary. The max deviation from the constant assumption is 0.42. Series values for 1990-1997 carry interpolated classification weights.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S502</t>
-        </is>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S503</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S515</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Total Product measures the gross output of productive and trading sectors combined. Book data (1948-1989) from Table E.2 is extended via BEA GDPbyIndustry (1997-2024) using growth-rate splicing at 1997.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SIC-to-NAICS classification break at 1997 splice point (see [internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1990-1996 gap requires interpolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trading sector boundary (wholesale vs retail) may shift under NAICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S502</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S503</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S515</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>BEA_GDPbyInd</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. GDP by Industry. https://apps.bea.gov/iTable/</t>
         </is>
@@ -2056,11 +3010,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -2152,91 +3106,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>BEA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>growth_rate</t>
+          <t>1997</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>growth_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S501-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S501-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5 (The Marxian Categories: Empirical Estimates), Appendix H.1 (pp. 324-327); revenue-side cross-check Appendix E.2 (p. 310, 1948-1961 subset)", "shaikh_appendix_ref": "Appendix H.1 column TP_star (1948-1989); Appendix E.2 column TP_star (1948-1961, duplicate-source validation); Figures 5.4, 5.6, 9.1, 9.2", "extension_source": "BEA GDP-by-Industry, value-added series for productive-sector NAICS industries (S501-B subseries; productive/unproductive concordance per docs/methodology/productive_classification_NAICS.md)", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "Total Product TP* is the Marxian measure of total value produced in the productive economy (M'_p + GFP). Both eras directly observe the same construct -- gross value generated in productive industries -- but under different industrial classifications (SIC vs NAICS). Growth-rate splice is appropriate per the Anu Extension Standard because the underlying construct is observed in both eras and is not itself a derived ratio. The SIC&lt;-&gt;NAICS concordance for productive/unproductive partitioning is the only methodological adjustment.", "vintage_note": "Book-period TP* is computed on SIC-based BEA NIPA + IO tables; extension is on post-1997 NAICS GDP-by-Industry. The 1990-1996 gap is bridged log-linearly between the 1989 book endpoint and the 1997 BEA NAICS endpoint (documented as methodological adjustment M04_S501). BEA comprehensive revisions (1999, 2003, 2009, 2013, 2018) may alter pre-1997 NIPA values; book values are frozen at the book's vintage.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 446.21, "1958": 711.67, "1961": 811.42}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0, 50000]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S501.xlsx
+++ b/extenbooks/S501.xlsx
@@ -589,10 +589,10 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>596.6</v>
+        <v>596.63</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>596.6</v>
+        <v>596.63</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
@@ -2522,7 +2522,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>- `ES1401` (Mohun 2005 productive output): independent reconstruction using a different productive/unproductive boundary.</t>
+          <t>- `XS1401` (Mohun 2005 productive output): independent reconstruction using a different productive/unproductive boundary.</t>
         </is>
       </c>
     </row>
@@ -3010,10 +3010,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3281,6 +3281,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S501.xlsx
+++ b/extenbooks/S501.xlsx
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
     </row>
